--- a/consent_forms/035_media_release_and_personal_injury_waiver--consent_forms.xlsx
+++ b/consent_forms/035_media_release_and_personal_injury_waiver--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Witness1</t>
+          <t>Witness1 Last Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Witness1</t>
+          <t>Witness1 Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Witness1</t>
+          <t>Witness1 Phone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Witness2</t>
+          <t>Witness2 Last Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Witness2</t>
+          <t>Witness2 Email</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Witness2</t>
+          <t>Witness2 Phone</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Witness3</t>
+          <t>Witness3 Last Name</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Witness3</t>
+          <t>Witness3 Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Witness3</t>
+          <t>Witness3 Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>media_usage</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Media usage</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>release_of_liability_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,27 +1182,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>medical_condition_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
